--- a/docs/策划/项目开发需求计划表.xlsx
+++ b/docs/策划/项目开发需求计划表.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L272"/>
+  <dimension ref="A1:L274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/backend/发版与热更策略.md</t>
+          <t>docs/策划/规格/后端/发版与热更策略.md</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/策划/规格/数据运维/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/data-ops/数据平台-Phase2-稳定增长.md</t>
+          <t>docs/策划/规格/数据运维/数据平台-Phase2-稳定增长.md</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>docs/archive/2026-10-26/retired/planning/specs/C-调优与状态机.md</t>
+          <t>docs/归档/2026-10-26/废弃/策划/规格/C-调优与状态机.md</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>docs/archive/2026-10-26/retired/planning/specs/状态机需求描述.md</t>
+          <t>docs/归档/2026-10-26/废弃/策划/规格/状态机需求描述.md</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/排行榜-入口与领奖台改版.md</t>
+          <t>docs/策划/规格/玩法/排行榜-入口与领奖台改版.md</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>P0-P5总表；见分阶段清单</t>
+          <t>2026-10-29 不再作为排期总表。P0～P2 已实现的记录保留，P5 仍单独存在</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
+          <t>docs/策划/规格/桌面端/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
+          <t>docs/策划/规格/桌面端/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
+          <t>docs/策划/规格/桌面端/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Tile·相机·序列帧；承接REF-SCENE-1</t>
+          <t>2026-10-29 不再做等距 Tile 场景。现有桌面鱼塘场景不按本阶段重做</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
+          <t>docs/策划/规格/桌面端/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity移植-分阶段需求清单.md</t>
+          <t>docs/策划/规格/桌面端/Unity移植-分阶段需求清单.md</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/roadmaps/phase2-开发计划.md</t>
+          <t>docs/策划/规格/路线图/phase2-开发计划.md</t>
         </is>
       </c>
       <c r="J124" s="3" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-进塘首帧状态与演示降级.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-进塘首帧状态与演示降级.md</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-每日额度单一口径重构.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-每日额度单一口径重构.md</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-进塘与钓鱼剩余展示回归.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-进塘与钓鱼剩余展示回归.md</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端独立游戏转型计划.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端独立游戏转型计划.md</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端产品定位与信息架构.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端产品定位与信息架构.md</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam身份账号绑定与安全会话.md</t>
+          <t>docs/策划/规格/桌面端/Steam身份账号绑定与安全会话.md</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam好友Lobby邀请与鱼塘映射.md</t>
+          <t>docs/策划/规格/桌面端/Steam好友Lobby邀请与鱼塘映射.md</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/空鱼塘休眠与生态离线补算.md</t>
+          <t>docs/策划/规格/玩法/空鱼塘休眠与生态离线补算.md</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Unity Windows桌面端基础壳.md</t>
+          <t>docs/策划/规格/桌面端/Unity Windows桌面端基础壳.md</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-桌面端关闭后进程残留.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-桌面端关闭后进程残留.md</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-SteamLobby创建权限与状态残留.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-SteamLobby创建权限与状态残留.md</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>docs/archive/2026-10-26/retired/planning/specs/Steam Lobby生命周期与邀请反馈优化.md</t>
+          <t>docs/归档/2026-10-26/废弃/策划/规格/Steam Lobby生命周期与邀请反馈优化.md</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面宠物UI需求拆分.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面宠物UI需求拆分.md</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面Overlay场景布局管线.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面Overlay场景布局管线.md</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-09AOverlay玩家右键菜单.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-09AOverlay玩家右键菜单.md</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-09BOverlay悬停状态与钓鱼时长.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-09BOverlay悬停状态与钓鱼时长.md</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-09COverlay鱼塘聊天气泡与输入.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-09COverlay鱼塘聊天气泡与输入.md</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-09DOverlay布局与角色表现优化.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-09DOverlay布局与角色表现优化.md</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端公网联调与服务器地址配置.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端公网联调与服务器地址配置.md</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>docs/archive/2026-10-26/retired/planning/specs/Steam桌面端本机公网映射联调.md</t>
+          <t>docs/归档/2026-10-26/废弃/策划/规格/Steam桌面端本机公网映射联调.md</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>方案已就绪(Windows手册)；实施可暂缓；上云仅改server.json；见docs/ops/windows-cloud-deploy.md</t>
+          <t>方案已就绪(Windows手册)；实施可暂缓；上云仅改server.json；见docs/运维/windows-cloud-deploy.md</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端云服务器联调保留.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端云服务器联调保留.md</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓鱼玩法扩展-v0.7-Epic.md</t>
+          <t>docs/策划/规格/玩法/钓鱼玩法扩展-v0.7-Epic.md</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/鱼塘分级与玩家成长.md</t>
+          <t>docs/策划/规格/玩法/鱼塘分级与玩家成长.md</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓具与鱼饵配置.md</t>
+          <t>docs/策划/规格/玩法/钓具与鱼饵配置.md</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08A2世界地图分区与进塘扣费.md</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/禁止钓鱼塘巡警事件.md</t>
+          <t>docs/策划/规格/玩法/禁止钓鱼塘巡警事件.md</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓位点位线索文字泡.md</t>
+          <t>docs/策划/规格/玩法/钓位点位线索文字泡.md</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-新手引导本地教学关.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-新手引导本地教学关.md</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-玩法Debug菜单.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-玩法Debug菜单.md</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/回鱼机制.md</t>
+          <t>docs/策划/规格/玩法/回鱼机制.md</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/打窝机制.md</t>
+          <t>docs/策划/规格/玩法/打窝机制.md</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓鱼相册与成就.md</t>
+          <t>docs/策划/规格/玩法/钓鱼相册与成就.md</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/双价塘与自动回鱼.md</t>
+          <t>docs/策划/规格/玩法/双价塘与自动回鱼.md</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-日额度满后仍可开钓.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-日额度满后仍可开钓.md</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>准入 purple/0.75 统一；回鱼金=卖价×1.5；仅收费塘可回；不达标留包</t>
+          <t>历史口径：紫品/体长 75%、金×1.5；准入已由 FEAT-RETURN-05 回鱼体重分档取代</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/回鱼规则调优.md</t>
+          <t>docs/归档/2026-10-26/替代/策划/规格/回鱼规则调优.md</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/塘生态数值表驱动.md</t>
+          <t>docs/策划/规格/玩法/塘生态数值表驱动.md</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/中国鱼种与区域分布.md</t>
+          <t>docs/策划/规格/玩法/中国鱼种与区域分布.md</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓位标签与线索库-v2.md</t>
+          <t>docs/策划/规格/玩法/钓位标签与线索库-v2.md</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓位标签地形微调.md</t>
+          <t>docs/策划/规格/玩法/钓位标签地形微调.md</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/线索文案策划审校.md</t>
+          <t>docs/策划/规格/玩法/线索文案策划审校.md</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓位鱼情联动线索.md</t>
+          <t>docs/策划/规格/玩法/钓位鱼情联动线索.md</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/自动回鱼体验闭环.md</t>
+          <t>docs/策划/规格/玩法/自动回鱼体验闭环.md</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-Debug鱼塘钓位查看.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-Debug鱼塘钓位查看.md</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/回鱼体重分档.md</t>
+          <t>docs/策划/规格/玩法/回鱼体重分档.md</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/塘人口与品质权重调参.md</t>
+          <t>docs/策划/规格/玩法/塘人口与品质权重调参.md</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面Overlay分塘底图与HUD同步.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面Overlay分塘底图与HUD同步.md</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-13OverlayHUD聊天栏与预制体对齐.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-13OverlayHUD聊天栏与预制体对齐.md</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-13AOverlay场景边缘半透明渐隐.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-13AOverlay场景边缘半透明渐隐.md</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-13BOverlay宠物标签右键与登录窗.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-13BOverlay宠物标签右键与登录窗.md</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-13COverlay打窝HUD收口.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-13COverlay打窝HUD收口.md</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-14Overlay透明点击穿透回归.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-14Overlay透明点击穿透回归.md</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-14AOverlay钓位座位图.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-14AOverlay钓位座位图.md</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-14BOverlay横轴场景平移.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-14BOverlay横轴场景平移.md</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-14COverlayHUD正式素材与文字对齐.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-14COverlayHUD正式素材与文字对齐.md</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>取消头顶相位字；小图标；圆环套在64猫身外圈；时长仍仅悬停</t>
+          <t>历史：圆环套猫、等鱼常驻图标。现行头顶状态见 STEAM-DESKTOP-14E</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-14DOverlay宠物状态图标与上钩圆环.md</t>
+          <t>docs/归档/2026-10-26/替代/策划/规格/Steam桌面端-14DOverlay宠物状态图标与上钩圆环.md</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-15Overlay钓鱼栏按钮时序.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-15Overlay钓鱼栏按钮时序.md</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-16Overlay窗口视口缩放.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-16Overlay窗口视口缩放.md</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-17占用座位不可顶机器人.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-17占用座位不可顶机器人.md</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Overlay形象进游戏不恢复.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Overlay形象进游戏不恢复.md</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Overlay打窝按钮剩余口数.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Overlay打窝按钮剩余口数.md</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Overlay悬停与右键菜单指针命中.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Overlay悬停与右键菜单指针命中.md</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-18Overlay悬停浮窗条数与hint定位.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-18Overlay悬停浮窗条数与hint定位.md</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-14EOverlay头顶状态图标与进度环.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-14EOverlay头顶状态图标与进度环.md</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-19咬钩结算弹窗.md</t>
+          <t>docs/归档/2026-10-26/替代/策划/规格/Steam桌面端-19咬钩结算弹窗.md</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/橘猫钓鱼动画接入Overlay.md</t>
+          <t>docs/策划/规格/桌面端/橘猫钓鱼动画接入Overlay.md</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12945,7 +12945,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG-46成就列表当前进度.md</t>
+          <t>docs/策划/规格/缺陷/BUG-46成就列表当前进度.md</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Cozy桌面页还原.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Cozy桌面页还原.md</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-OverlayHUD布局与交互.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-OverlayHUD布局与交互.md</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Unity自己钓鱼表现权威.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Unity自己钓鱼表现权威.md</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-默认头像目录与运行白名单不一致.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-默认头像目录与运行白名单不一致.md</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-Overlay阶段切换卡帧与收杆重播.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-Overlay阶段切换卡帧与收杆重播.md</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-20主窗口固定分辨率.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-20主窗口固定分辨率.md</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13795,7 +13795,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-桌面设置世界首页与装备图.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-桌面设置世界首页与装备图.md</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-桌面鱼塘与设置信息.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-桌面鱼塘与设置信息.md</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-21猫咪钓鱼手账动效.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-21猫咪钓鱼手账动效.md</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>docs/planning/specs/bugs/BUG修复-手账翻页标签与排行榜.md</t>
+          <t>docs/策划/规格/缺陷/BUG修复-手账翻页标签与排行榜.md</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14189,12 +14189,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>扩展十角色14种动作轨迹采样，发力循环接缝、脚底固定微转、手持鱼保护；鱼下沉64原画单位；复用PNG/原时长；Windows待验收</t>
+          <t>十一角色14动作；10/30抛竿扩为6帧/600ms，追加过顶与前甩道具关键帧；三端PNG/清单/入水标记同步；22项核心测试、5项资源回归、19项音效标记与616次Web渲染通过；Windows待验收</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22鱼塘表现修复与后续迭代.md</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22H钓鱼特效设计.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22H钓鱼特效设计.md</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>v5配乐与46条v3音效及猫声已采用并应用；旧版音频和无效工具已清理，来源许可留档；Unity-WPF已接入，Windows画声延迟待实测</t>
+          <t>钓鱼场景关闭BGM与按钮音，分塘湖面与连续交融风叶已采用；保留动作声/猫叫；10月31日首页原创BGM《晴窗小憩》候选加入总页，待试听采用，正式v5暂保留；Windows画声延迟待实测</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22I声音体验设计.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22I声音体验设计.md</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14489,14 +14489,14 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -14531,17 +14531,22 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>地图方案v1：三栏尺寸、点位/标签避让、筛选/缩放、档位费用确认；地理文案改由 WORLD-CAT-01 提供，本项仍未实现</t>
+          <t>方案已归档，不再开发。现行世界地图为 08A／08A2</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22J世界地图设计.md</t>
+          <t>docs/归档/2026-10-26/替代/策划/规格/Steam桌面端-22J世界地图设计.md</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -14583,12 +14588,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Unity/Overlay固定脚底有界呼吸、握竿同步及鱼线端点；Unity相关203/203、运动24/24；Windows待验收</t>
+          <t>10/30按确认预览将呼吸提升至清醒±2.2%/睡着±2.8%，Unity/Overlay固定脚底、握竿及线端；Unity187/187、Overlay7/7；总预览#rest；Windows待验收</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14598,7 +14603,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14640,12 +14645,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>默认30分钟，可配置；服务器持久化/直接逃鱼、本人触碰唤醒、11角色局部闭眼；服务端35/35；Windows待验收</t>
+          <t>10/30新增6.4秒八阶段低头/停顿/抬头，Unity/Overlay连续形变；保留默认30分钟与服务器权威唤醒/脱钩；统一总预览#rest；Windows待验收</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14655,7 +14660,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14707,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
+          <t>docs/策划/规格/桌面端/Steam桌面端-22KLM呼吸瞌睡与狸花猫.md</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14759,7 +14764,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>docs/planning/specs/world/猫咪世界观与场景描述.md</t>
+          <t>docs/策划/规格/世界观/猫咪世界观与场景描述.md</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14811,7 +14816,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>docs/planning/specs/gameplay/钓鱼体长体重步进与公式评判.md</t>
+          <t>docs/策划/规格/玩法/钓鱼体长体重步进与公式评判.md</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -14823,962 +14828,1073 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
+          <t>已废弃</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>OPS-HOT-1</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>运维</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>桌面资源与数值热更</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>hotfix</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>不再做。客户端整包上 Steam 后由商店更新内容，不需要单独的资源或数值热更通道</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/后端/桌面资源与数值热更.md</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="84" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
           <t>已确认</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>OPS-HOT-1</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>运维</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>桌面资源与数值热更</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>hotfix</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>FISH-BREAK-01</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>钓鱼断线与断竿表现</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>不重做 OPS-RELEASE-1。准备 Overlay 资源包和钓鱼数值表的不停服替换与回滚，不热更 exe</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/backend/桌面资源与数值热更.md</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>自然脱钩内分配断线表现，不增加总失败率；成功超规格累计满次后折断竿，保留当次鱼获；补权威结果、去重与备用竿衔接</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/玩法/钓鱼断线与断竿表现.md</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258" ht="84" customHeight="1">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>FISH-SCALE-01</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>上钩鱼尺寸与实际体长映射</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>后续迭代</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>0.02–50m 十八控制点连续映射到8–204标准逻辑px；40m现行上限192px；跨动作锁定、嘴部/持鱼锚点、水面裁剪与巨物溢出</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/玩法/上钩鱼尺寸与体长映射.md</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K258" s="3" t="inlineStr"/>
+    </row>
+    <row r="259" ht="84" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07A</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C259" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D259" s="3" t="inlineStr">
         <is>
           <t>桌面宠物主视图与鱼塘入口</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H259" s="3" t="inlineStr">
         <is>
           <t>显示自己的 2D 猫咪、钓鱼状态和鱼塘入口；采用序列帧+状态机，复用已完成桌面壳</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
+      <c r="I259" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J259" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="K259" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
+    <row r="260" ht="84" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07B</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C260" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D260" s="3" t="inlineStr">
         <is>
           <t>2D 鱼塘环境与自己的猫咪</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H260" s="3" t="inlineStr">
         <is>
           <t>显示池塘环境、钓位、自己的宠物和钓鱼表现</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
+      <c r="I260" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J260" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="K260" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
+    <row r="261" ht="84" customHeight="1">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07C</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C261" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D261" s="3" t="inlineStr">
         <is>
           <t>同塘玩家宠物与状态同步</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H261" s="3" t="inlineStr">
         <is>
           <t>在 Overlay 渲染 pond_user_joined/left/updated；128×128 统一序列帧；fishingPhase→petVisualState；IPC 不传图、不新开协议</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
+      <c r="I261" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J261" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
+      <c r="K261" s="3" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
+    <row r="262" ht="84" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07D</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C262" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D262" s="3" t="inlineStr">
         <is>
           <t>桌面宠物右键菜单</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H262" s="3" t="inlineStr">
         <is>
           <t>在产品窗口/宠物区域提供鱼塘、好友、背包、图鉴、设置、托盘和退出入口</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
+      <c r="I262" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J262" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K262" s="3" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
+    <row r="263" ht="84" customHeight="1">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07E</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C263" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D263" s="3" t="inlineStr">
         <is>
           <t>桌面宠物主窗口功能页签</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H263" s="3" t="inlineStr">
         <is>
           <t>好友/聊天、背包、图鉴、设置为主窗口页签；Overlay 菜单切页且主窗口高于 Overlay；不用功能弹窗</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端Web功能对齐设计.md</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
+      <c r="I263" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端Web功能对齐设计.md</t>
+        </is>
+      </c>
+      <c r="J263" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="K263" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
+    <row r="264" ht="84" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07F</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C264" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D264" s="3" t="inlineStr">
         <is>
           <t>桌面宠物主流程与恢复验收</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H264" s="3" t="inlineStr">
         <is>
           <t>串联登录、进塘、挂机、通知、托盘、收鱼、断线恢复并完成 Windows 验收</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面宠物与多人鱼塘表现层.md</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
+      <c r="I264" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面宠物与多人鱼塘表现层.md</t>
+        </is>
+      </c>
+      <c r="J264" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="K264" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
+    <row r="265" ht="84" customHeight="1">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-07G</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C265" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D265" s="3" t="inlineStr">
         <is>
           <t>原生桌面宠物 Overlay</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H265" s="3" t="inlineStr">
         <is>
           <t>独立 WPF/Win32 Overlay；不启动第二个 Unity Player；通过 Named Pipe 接收状态并发送命令</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam原生桌面宠物Overlay.md</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
+      <c r="I265" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam原生桌面宠物Overlay.md</t>
+        </is>
+      </c>
+      <c r="J265" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K265" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
+    <row r="266" ht="84" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08A</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C266" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D266" s="3" t="inlineStr">
         <is>
           <t>世界地图与鱼塘选择</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H266" s="3" t="inlineStr">
         <is>
           <t>主窗口超大地图 Image：拖动/滚轮缩放/边界；pondId 坐标绑定；点击进塘并显示 Overlay</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08A世界地图与鱼塘选择.md</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
+      <c r="I266" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08A世界地图与鱼塘选择.md</t>
+        </is>
+      </c>
+      <c r="J266" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="K266" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
+    <row r="267" ht="84" customHeight="1">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08B</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C267" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D267" s="3" t="inlineStr">
         <is>
           <t>商店与装备</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H267" s="3" t="inlineStr">
         <is>
           <t>PanelShop：鱼饵/渔具购买与装备；金币库存以服务端为准；Overlay 只 menu_shop 切页</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08B商店与装备.md</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08B商店与装备.md</t>
+        </is>
+      </c>
+      <c r="J267" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="K267" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
+    <row r="268" ht="84" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08C</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C268" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D268" s="3" t="inlineStr">
         <is>
           <t>动态墙与好友动态</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H268" s="3" t="inlineStr">
         <is>
           <t>PanelSocialFeed：公共/好友动态、分页加载、动态卡片 Prefab、点赞、评论、删除评论；不塞进 PanelSocial</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08C动态墙与好友动态.md</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
+      <c r="I268" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08C动态墙与好友动态.md</t>
+        </is>
+      </c>
+      <c r="J268" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K268" s="3" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
+    <row r="269" ht="84" customHeight="1">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08D</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="C269" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D269" s="3" t="inlineStr">
         <is>
           <t>排行榜</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="H269" s="3" t="inlineStr">
         <is>
           <t>PanelLeaderboard：日/周/鱼塘/稀有四榜；Top3 固定 Image 领奖台；4 名起纵向滚动；分数以服务端为准</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08D排行榜.md</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
+      <c r="I269" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08D排行榜.md</t>
+        </is>
+      </c>
+      <c r="J269" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="K269" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
+    <row r="270" ht="84" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08E</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
+      <c r="C270" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D270" s="3" t="inlineStr">
         <is>
           <t>个人中心与资料编辑</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
+      <c r="H270" s="3" t="inlineStr">
         <is>
           <t>PanelProfile/Edit：昵称头像展示鱼获；不改 SteamID、不迁移旧档</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08E个人中心与资料编辑.md</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
+      <c r="I270" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08E个人中心与资料编辑.md</t>
+        </is>
+      </c>
+      <c r="J270" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
+      <c r="K270" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
+    <row r="271" ht="84" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08F</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C271" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D271" s="3" t="inlineStr">
         <is>
           <t>好友列表与申请 Prefab</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="H271" s="3" t="inlineStr">
         <is>
           <t>独立 PanelFriends；修复接受/拒绝重叠不可点；不与 PanelSocial 双开好友 UI</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08F好友列表与申请Prefab.md</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
+      <c r="I271" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08F好友列表与申请Prefab.md</t>
+        </is>
+      </c>
+      <c r="J271" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="K271" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
+    <row r="272" ht="84" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08G</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C272" s="3" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D272" s="3" t="inlineStr">
         <is>
           <t>Overlay 钓鱼操作栏</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
+      <c r="H272" s="3" t="inlineStr">
         <is>
           <t>Overlay 底部选钓位/开始/收杆/领鱼获；Pipe 发命令；Unity/Node 保留权威</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
+      <c r="I272" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08GOverlay钓鱼操作栏.md</t>
+        </is>
+      </c>
+      <c r="J272" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="K272" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
+    <row r="273" ht="84" customHeight="1">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08H</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C273" s="3" t="inlineStr">
         <is>
           <t>工程</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D273" s="3" t="inlineStr">
         <is>
           <t>全量 UI 预制体化与动态内容组件</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H273" s="3" t="inlineStr">
         <is>
           <t>壳层、功能页、列表行和 Grid item 全部使用合法 Prefab；运行时代码只绑定数据和事件</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08H全量UI预制体化.md</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08H全量UI预制体化.md</t>
+        </is>
+      </c>
+      <c r="J273" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="K273" s="3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>已实现</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
+    <row r="274" ht="84" customHeight="1">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
         <is>
           <t>STEAM-DESKTOP-08I</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C274" s="3" t="inlineStr">
         <is>
           <t>Bug修复</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D274" s="3" t="inlineStr">
         <is>
           <t>鱼塘退出与跨塘切换优化</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>v1.0-steam-desktop</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
+      <c r="H274" s="3" t="inlineStr">
         <is>
           <t>Overlay 点击钓位直接入座；新增离席/退出鱼塘；收杆领鱼离席后跨塘切换；修复隐藏主窗口时 5 FPS 导致的 ACK 延迟，增加 ACK 优先队列、持久状态序号、重复状态丢弃及三段链路时间戳验收</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>docs/planning/specs/desktop/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
+      <c r="I274" s="3" t="inlineStr">
+        <is>
+          <t>docs/策划/规格/桌面端/Steam桌面端-08I鱼塘退出与跨塘切换优化.md</t>
+        </is>
+      </c>
+      <c r="J274" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="K274" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -21590,7 +21706,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -21778,7 +21894,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>已定稿</t>
+          <t>已废弃</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
